--- a/BVSimulationFiles/40.xlsx
+++ b/BVSimulationFiles/40.xlsx
@@ -6,11 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet1 Copy" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1 Copy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1 Copy Copy" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -414,75 +414,39 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.0004958333333333333</v>
+        <v>0.0009916666666666665</v>
       </c>
       <c r="D1" t="n">
-        <v>0.0009916666666666665</v>
+        <v>0.001983333333333333</v>
       </c>
       <c r="E1" t="n">
-        <v>0.0014875</v>
+        <v>0.002974999999999999</v>
       </c>
       <c r="F1" t="n">
-        <v>0.001983333333333333</v>
+        <v>0.003966666666666666</v>
       </c>
       <c r="G1" t="n">
-        <v>0.002479166666666666</v>
+        <v>0.004958333333333333</v>
       </c>
       <c r="H1" t="n">
-        <v>0.002974999999999999</v>
+        <v>0.005949999999999999</v>
       </c>
       <c r="I1" t="n">
-        <v>0.003470833333333333</v>
+        <v>0.006941666666666665</v>
       </c>
       <c r="J1" t="n">
-        <v>0.003966666666666666</v>
+        <v>0.007933333333333332</v>
       </c>
       <c r="K1" t="n">
-        <v>0.004462499999999999</v>
+        <v>0.008924999999999999</v>
       </c>
       <c r="L1" t="n">
-        <v>0.004958333333333333</v>
+        <v>0.009916666666666666</v>
       </c>
       <c r="M1" t="n">
-        <v>0.005454166666666666</v>
+        <v>0.01090833333333333</v>
       </c>
       <c r="N1" t="n">
-        <v>0.005949999999999999</v>
-      </c>
-      <c r="O1" t="n">
-        <v>0.006445833333333332</v>
-      </c>
-      <c r="P1" t="n">
-        <v>0.006941666666666665</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>0.007437499999999999</v>
-      </c>
-      <c r="R1" t="n">
-        <v>0.007933333333333332</v>
-      </c>
-      <c r="S1" t="n">
-        <v>0.008429166666666665</v>
-      </c>
-      <c r="T1" t="n">
-        <v>0.008924999999999999</v>
-      </c>
-      <c r="U1" t="n">
-        <v>0.009420833333333331</v>
-      </c>
-      <c r="V1" t="n">
-        <v>0.009916666666666666</v>
-      </c>
-      <c r="W1" t="n">
-        <v>0.0104125</v>
-      </c>
-      <c r="X1" t="n">
-        <v>0.01090833333333333</v>
-      </c>
-      <c r="Y1" t="n">
-        <v>0.01140416666666666</v>
-      </c>
-      <c r="Z1" t="n">
         <v>0.0119</v>
       </c>
     </row>
